--- a/Excels/Excels/B-Battle_战斗表.xlsx
+++ b/Excels/Excels/B-Battle_战斗表.xlsx
@@ -4,7 +4,7 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unit" sheetId="1" state="visible" r:id="rId1"/>
@@ -31,7 +31,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <name val="Noto Sans SC"/>
       <charset val="134"/>
@@ -71,11 +71,8 @@
       <color theme="1"/>
       <sz val="11"/>
     </font>
-    <font>
-      <b val="1"/>
-    </font>
   </fonts>
-  <fills count="10">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -106,26 +103,6 @@
         <bgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D9EAF7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E2F0D9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -146,7 +123,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -171,6 +148,12 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -193,25 +176,10 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -516,268 +484,331 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="7.7734375" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="9.1" customWidth="1" style="8" min="1" max="6"/>
-    <col width="38.21" customWidth="1" style="8" min="7" max="7"/>
-    <col width="17.29" customWidth="1" style="8" min="8" max="8"/>
-    <col width="13.65" customWidth="1" style="8" min="9" max="9"/>
+    <col width="9.1" customWidth="1" style="10" min="1" max="6"/>
+    <col width="38.21" customWidth="1" style="10" min="7" max="7"/>
+    <col width="17.29" customWidth="1" style="10" min="8" max="8"/>
+    <col width="13.65" customWidth="1" style="10" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="9">
-      <c r="A1" s="10" t="inlineStr">
+    <row r="1" ht="15" customHeight="1" s="11">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>##var</t>
         </is>
       </c>
-      <c r="B1" s="10" t="inlineStr">
+      <c r="B1" s="12" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="C1" s="10" t="inlineStr">
+      <c r="C1" s="12" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="D1" s="10" t="inlineStr">
+      <c r="D1" s="12" t="inlineStr">
         <is>
           <t>radius</t>
         </is>
       </c>
-      <c r="E1" s="10" t="inlineStr">
+      <c r="E1" s="12" t="inlineStr">
         <is>
           <t>camp</t>
         </is>
       </c>
-      <c r="F1" s="10" t="inlineStr">
+      <c r="F1" s="12" t="inlineStr">
         <is>
           <t>layer</t>
         </is>
       </c>
-      <c r="G1" s="10" t="inlineStr">
+      <c r="G1" s="12" t="inlineStr">
         <is>
           <t>attrs</t>
         </is>
       </c>
-      <c r="H1" s="10" t="inlineStr">
+      <c r="H1" s="12" t="inlineStr">
         <is>
           <t>defaultSkills</t>
         </is>
       </c>
-      <c r="I1" s="10" t="inlineStr">
+      <c r="I1" s="12" t="inlineStr">
         <is>
           <t>renderKey</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1" s="9">
-      <c r="A2" s="11" t="inlineStr">
+    <row r="2" ht="15" customHeight="1" s="11">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>##type</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="C2" s="11" t="inlineStr">
+      <c r="C2" s="13" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="D2" s="11" t="inlineStr">
+      <c r="D2" s="13" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="E2" s="11" t="inlineStr">
+      <c r="E2" s="13" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F2" s="11" t="inlineStr">
+      <c r="F2" s="13" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="G2" s="11" t="inlineStr">
+      <c r="G2" s="13" t="inlineStr">
         <is>
           <t>(array#sep=|),(Attr.AttributePair#sep=,)</t>
         </is>
       </c>
-      <c r="H2" s="11" t="inlineStr">
+      <c r="H2" s="13" t="inlineStr">
         <is>
           <t>(array#sep=|),int</t>
         </is>
       </c>
-      <c r="I2" s="11" t="inlineStr">
+      <c r="I2" s="13" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1" s="9">
-      <c r="A3" s="12" t="inlineStr">
+    <row r="3" ht="15" customHeight="1" s="11">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>##group</t>
         </is>
       </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="C3" s="12" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="D3" s="12" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="E3" s="12" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="F3" s="12" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="G3" s="12" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="H3" s="12" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="I3" s="12" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1" s="9">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="C3" s="14" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="D3" s="14" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="E3" s="14" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="F3" s="14" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="G3" s="14" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="H3" s="14" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="I3" s="14" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1" s="11">
+      <c r="A4" s="15" t="inlineStr">
         <is>
           <t>##</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B4" s="16" t="inlineStr">
         <is>
           <t>单位id</t>
         </is>
       </c>
-      <c r="C4" s="14" t="inlineStr">
+      <c r="C4" s="16" t="inlineStr">
         <is>
           <t>单位名</t>
         </is>
       </c>
-      <c r="D4" s="14" t="inlineStr">
+      <c r="D4" s="16" t="inlineStr">
         <is>
           <t>碰撞半径</t>
         </is>
       </c>
-      <c r="E4" s="14" t="inlineStr">
+      <c r="E4" s="16" t="inlineStr">
         <is>
           <t>默认阵营</t>
         </is>
       </c>
-      <c r="F4" s="14" t="inlineStr">
+      <c r="F4" s="16" t="inlineStr">
         <is>
           <t>层级</t>
         </is>
       </c>
-      <c r="G4" s="14" t="inlineStr">
+      <c r="G4" s="16" t="inlineStr">
         <is>
           <t>初始属性</t>
         </is>
       </c>
-      <c r="H4" s="14" t="inlineStr">
+      <c r="H4" s="16" t="inlineStr">
         <is>
           <t>默认技能</t>
         </is>
       </c>
-      <c r="I4" s="14" t="inlineStr">
+      <c r="I4" s="16" t="inlineStr">
         <is>
           <t>表现资源key</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="9">
-      <c r="B5" s="8" t="n">
+    <row r="5" ht="15" customHeight="1" s="11">
+      <c r="B5" s="10" t="n">
         <v>1001</v>
       </c>
-      <c r="C5" s="8" t="inlineStr">
-        <is>
-          <t>玩家</t>
-        </is>
-      </c>
-      <c r="D5" s="8" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="E5" s="8" t="n">
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>弓箭手</t>
+        </is>
+      </c>
+      <c r="D5" s="10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E5" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="F5" s="8" t="n">
+      <c r="F5" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="G5" s="15" t="inlineStr">
+      <c r="G5" s="17" t="inlineStr">
+        <is>
+          <t>102,500|105,500|101,50|103,10|104,300</t>
+        </is>
+      </c>
+      <c r="H5" s="10" t="n">
+        <v>2002</v>
+      </c>
+      <c r="I5" s="10" t="inlineStr">
+        <is>
+          <t>Character_1_AnimationVit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1" s="11">
+      <c r="B6" s="10" t="n">
+        <v>1002</v>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>野蛮人</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E6" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="17" t="inlineStr">
         <is>
           <t>102,1000|105,1000|101,50|103,10|104,300</t>
         </is>
       </c>
-      <c r="H5" s="15" t="inlineStr">
-        <is>
-          <t>2001|2002</t>
-        </is>
-      </c>
-      <c r="I5" s="15" t="inlineStr">
-        <is>
-          <t>Cat</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1" s="9">
-      <c r="B6" s="8" t="n">
-        <v>1101</v>
-      </c>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>小怪</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="E6" s="8" t="n">
+      <c r="H6" s="17" t="n">
+        <v>2001</v>
+      </c>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>Character_2_AnimationVit</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1" s="11">
+      <c r="G7" s="17" t="n"/>
+    </row>
+    <row r="8" ht="15" customHeight="1" s="11">
+      <c r="B8" s="10" t="n">
+        <v>2001</v>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>野猫</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E8" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="F6" s="8" t="n">
+      <c r="F8" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="G6" s="15" t="inlineStr">
+      <c r="G8" s="17" t="inlineStr">
         <is>
           <t>102,300|105,300|101,20|103,3|104,220</t>
         </is>
       </c>
-      <c r="H6" s="15" t="inlineStr">
-        <is>
-          <t>2101</t>
-        </is>
-      </c>
-      <c r="I6" s="15" t="inlineStr">
-        <is>
-          <t>Dog</t>
+      <c r="H8" s="17" t="n">
+        <v>2001</v>
+      </c>
+      <c r="I8" s="17" t="inlineStr">
+        <is>
+          <t>Animal_Cat_AnimationVit</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1" s="11">
+      <c r="B9" s="10" t="n">
+        <v>2002</v>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>野狗</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E9" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="17" t="inlineStr">
+        <is>
+          <t>102,300|105,300|101,20|103,3|104,220</t>
+        </is>
+      </c>
+      <c r="H9" s="17" t="n">
+        <v>2001</v>
+      </c>
+      <c r="I9" s="17" t="inlineStr">
+        <is>
+          <t>Animal_Dog_AnimationVit</t>
         </is>
       </c>
     </row>
@@ -795,374 +826,403 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="7.7734375" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="9.1" customWidth="1" style="8" min="1" max="3"/>
-    <col width="10.92" customWidth="1" style="8" min="4" max="4"/>
-    <col width="10.01" customWidth="1" style="8" min="5" max="5"/>
-    <col width="10.92" customWidth="1" style="8" min="6" max="7"/>
-    <col width="21.84" customWidth="1" style="8" min="8" max="8"/>
-    <col width="22.76" customWidth="1" style="8" min="9" max="9"/>
-    <col width="21.84" customWidth="1" style="8" min="10" max="10"/>
-    <col width="29.11" customWidth="1" style="8" min="11" max="11"/>
+    <col width="9.1" customWidth="1" style="10" min="1" max="3"/>
+    <col width="10.92" customWidth="1" style="10" min="4" max="4"/>
+    <col width="10.01" customWidth="1" style="10" min="5" max="5"/>
+    <col width="10.92" customWidth="1" style="10" min="6" max="7"/>
+    <col width="21.84" customWidth="1" style="10" min="8" max="8"/>
+    <col width="22.76" customWidth="1" style="10" min="9" max="9"/>
+    <col width="21.84" customWidth="1" style="10" min="10" max="10"/>
+    <col width="29.11" customWidth="1" style="10" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="9">
-      <c r="A1" s="10" t="inlineStr">
+    <row r="1" ht="15" customHeight="1" s="11">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>##var</t>
         </is>
       </c>
-      <c r="B1" s="10" t="inlineStr">
+      <c r="B1" s="12" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="C1" s="10" t="inlineStr">
+      <c r="C1" s="12" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="D1" s="10" t="inlineStr">
+      <c r="D1" s="12" t="inlineStr">
         <is>
           <t>actionName</t>
         </is>
       </c>
-      <c r="E1" s="10" t="inlineStr">
+      <c r="E1" s="12" t="inlineStr">
         <is>
           <t>castPreMs</t>
         </is>
       </c>
-      <c r="F1" s="10" t="inlineStr">
+      <c r="F1" s="12" t="inlineStr">
         <is>
           <t>castBackMs</t>
         </is>
       </c>
-      <c r="G1" s="10" t="inlineStr">
+      <c r="G1" s="12" t="inlineStr">
         <is>
           <t>cooldownMs</t>
         </is>
       </c>
-      <c r="H1" s="10" t="inlineStr">
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>castRange</t>
+        </is>
+      </c>
+      <c r="I1" s="12" t="inlineStr">
         <is>
           <t>targetType</t>
         </is>
       </c>
-      <c r="I1" s="10" t="inlineStr">
+      <c r="J1" s="12" t="inlineStr">
         <is>
           <t>selectType</t>
         </is>
       </c>
-      <c r="J1" s="10" t="inlineStr">
+      <c r="K1" s="12" t="inlineStr">
         <is>
           <t>shape</t>
         </is>
       </c>
-      <c r="K1" s="10" t="inlineStr">
+      <c r="L1" s="12" t="inlineStr">
         <is>
           <t>effects</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1" s="9">
-      <c r="A2" s="11" t="inlineStr">
+    <row r="2" ht="15" customHeight="1" s="11">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>##type</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="C2" s="11" t="inlineStr">
+      <c r="C2" s="13" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="D2" s="11" t="inlineStr">
+      <c r="D2" s="13" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="E2" s="11" t="inlineStr">
+      <c r="E2" s="13" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F2" s="11" t="inlineStr">
+      <c r="F2" s="13" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="G2" s="11" t="inlineStr">
+      <c r="G2" s="13" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="H2" s="11" t="inlineStr">
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="I2" s="13" t="inlineStr">
         <is>
           <t>Battle.SkillTargetType</t>
         </is>
       </c>
-      <c r="I2" s="11" t="inlineStr">
+      <c r="J2" s="13" t="inlineStr">
         <is>
           <t>Battle.TargetSelectType</t>
         </is>
       </c>
-      <c r="J2" s="11" t="inlineStr">
+      <c r="K2" s="13" t="inlineStr">
         <is>
           <t>Battle.BattleShapeDesc</t>
         </is>
       </c>
-      <c r="K2" s="11" t="inlineStr">
+      <c r="L2" s="13" t="inlineStr">
         <is>
           <t>(array#sep=|),Battle.EffectRef</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1" s="9">
-      <c r="A3" s="12" t="inlineStr">
+    <row r="3" ht="15" customHeight="1" s="11">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>##group</t>
         </is>
       </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="C3" s="12" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="D3" s="12" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="E3" s="12" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="F3" s="12" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="G3" s="12" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="H3" s="12" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="I3" s="12" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="J3" s="12" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="K3" s="12" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1" s="9">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="C3" s="14" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="D3" s="14" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="E3" s="14" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="F3" s="14" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="G3" s="14" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="I3" s="14" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="J3" s="14" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="K3" s="14" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="L3" s="14" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1" s="11">
+      <c r="A4" s="15" t="inlineStr">
         <is>
           <t>##</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B4" s="16" t="inlineStr">
         <is>
           <t>技能id</t>
         </is>
       </c>
-      <c r="C4" s="14" t="inlineStr">
+      <c r="C4" s="16" t="inlineStr">
         <is>
           <t>技能名</t>
         </is>
       </c>
-      <c r="D4" s="14" t="inlineStr">
+      <c r="D4" s="16" t="inlineStr">
         <is>
           <t>动作名</t>
         </is>
       </c>
-      <c r="E4" s="14" t="inlineStr">
+      <c r="E4" s="16" t="inlineStr">
         <is>
           <t>前摇毫秒</t>
         </is>
       </c>
-      <c r="F4" s="14" t="inlineStr">
+      <c r="F4" s="16" t="inlineStr">
         <is>
           <t>后摇毫秒</t>
         </is>
       </c>
-      <c r="G4" s="14" t="inlineStr">
+      <c r="G4" s="16" t="inlineStr">
         <is>
           <t>冷却毫秒</t>
         </is>
       </c>
-      <c r="H4" s="14" t="inlineStr">
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>????</t>
+        </is>
+      </c>
+      <c r="I4" s="16" t="inlineStr">
         <is>
           <t>目标类型</t>
         </is>
       </c>
-      <c r="I4" s="14" t="inlineStr">
+      <c r="J4" s="16" t="inlineStr">
         <is>
           <t>选敌方式</t>
         </is>
       </c>
-      <c r="J4" s="14" t="inlineStr">
+      <c r="K4" s="16" t="inlineStr">
         <is>
           <t>范围形状</t>
         </is>
       </c>
-      <c r="K4" s="14" t="inlineStr">
+      <c r="L4" s="16" t="inlineStr">
         <is>
           <t>效果列表</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="9">
-      <c r="B5" s="8" t="n">
+    <row r="5" ht="15" customHeight="1" s="11">
+      <c r="B5" s="10" t="n">
         <v>2001</v>
       </c>
-      <c r="C5" s="8" t="inlineStr">
+      <c r="C5" s="10" t="inlineStr">
         <is>
           <t>普攻</t>
         </is>
       </c>
-      <c r="D5" s="15" t="inlineStr">
+      <c r="D5" s="17" t="inlineStr">
         <is>
           <t>attack</t>
         </is>
       </c>
-      <c r="E5" s="8" t="n">
+      <c r="E5" s="10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F5" s="10" t="n">
+        <v>200</v>
+      </c>
+      <c r="G5" s="10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I5" s="17" t="inlineStr">
+        <is>
+          <t>Enemy</t>
+        </is>
+      </c>
+      <c r="J5" s="17" t="inlineStr">
+        <is>
+          <t>Nearest</t>
+        </is>
+      </c>
+      <c r="K5" s="17" t="inlineStr">
+        <is>
+          <t>Circle,1.2,0,0,0,0,0</t>
+        </is>
+      </c>
+      <c r="L5" s="17" t="inlineStr">
+        <is>
+          <t>Damage,3001,10000</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1" s="11">
+      <c r="B6" s="10" t="n">
+        <v>2002</v>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>远程普攻</t>
+        </is>
+      </c>
+      <c r="D6" s="17" t="inlineStr">
+        <is>
+          <t>attack</t>
+        </is>
+      </c>
+      <c r="E6" s="10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F6" s="10" t="n">
         <v>300</v>
       </c>
-      <c r="F5" s="8" t="n">
+      <c r="G6" s="10" t="n">
+        <v>2000</v>
+      </c>
+      <c r="H6" t="n">
+        <v>8</v>
+      </c>
+      <c r="I6" s="17" t="inlineStr">
+        <is>
+          <t>Enemy</t>
+        </is>
+      </c>
+      <c r="J6" s="17" t="inlineStr">
+        <is>
+          <t>Nearest</t>
+        </is>
+      </c>
+      <c r="K6" s="17" t="inlineStr">
+        <is>
+          <t>Null,0,0,0,0,0,0</t>
+        </is>
+      </c>
+      <c r="L6" s="17" t="inlineStr">
+        <is>
+          <t>Projectile,6001,0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1" s="11">
+      <c r="B7" s="10" t="n">
+        <v>2101</v>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>怪物撕咬</t>
+        </is>
+      </c>
+      <c r="D7" s="17" t="inlineStr">
+        <is>
+          <t>attack</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="n">
+        <v>500</v>
+      </c>
+      <c r="F7" s="10" t="n">
         <v>200</v>
       </c>
-      <c r="G5" s="8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H5" s="15" t="inlineStr">
+      <c r="G7" s="10" t="n">
+        <v>1500</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" s="17" t="inlineStr">
         <is>
           <t>Enemy</t>
         </is>
       </c>
-      <c r="I5" s="15" t="inlineStr">
+      <c r="J7" s="17" t="inlineStr">
         <is>
           <t>Nearest</t>
         </is>
       </c>
-      <c r="J5" s="15" t="inlineStr">
-        <is>
-          <t>Circle,1.2,0,0,0,0,0</t>
-        </is>
-      </c>
-      <c r="K5" s="15" t="inlineStr">
-        <is>
-          <t>Damage,3001,10000</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1" s="9">
-      <c r="B6" s="8" t="n">
-        <v>2002</v>
-      </c>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>火球术</t>
-        </is>
-      </c>
-      <c r="D6" s="15" t="inlineStr">
-        <is>
-          <t>attack</t>
-        </is>
-      </c>
-      <c r="E6" s="8" t="n">
-        <v>400</v>
-      </c>
-      <c r="F6" s="8" t="n">
-        <v>300</v>
-      </c>
-      <c r="G6" s="8" t="n">
-        <v>2000</v>
-      </c>
-      <c r="H6" s="15" t="inlineStr">
-        <is>
-          <t>Enemy</t>
-        </is>
-      </c>
-      <c r="I6" s="15" t="inlineStr">
-        <is>
-          <t>Nearest</t>
-        </is>
-      </c>
-      <c r="J6" s="15" t="inlineStr">
-        <is>
-          <t>Null,0,0,0,0,0,0</t>
-        </is>
-      </c>
-      <c r="K6" s="15" t="inlineStr">
-        <is>
-          <t>Projectile,6001,0</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1" s="9">
-      <c r="B7" s="8" t="n">
-        <v>2101</v>
-      </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>怪物撕咬</t>
-        </is>
-      </c>
-      <c r="D7" s="15" t="inlineStr">
-        <is>
-          <t>attack</t>
-        </is>
-      </c>
-      <c r="E7" s="8" t="n">
-        <v>500</v>
-      </c>
-      <c r="F7" s="8" t="n">
-        <v>200</v>
-      </c>
-      <c r="G7" s="8" t="n">
-        <v>1500</v>
-      </c>
-      <c r="H7" s="15" t="inlineStr">
-        <is>
-          <t>Enemy</t>
-        </is>
-      </c>
-      <c r="I7" s="15" t="inlineStr">
-        <is>
-          <t>Nearest</t>
-        </is>
-      </c>
-      <c r="J7" s="15" t="inlineStr">
+      <c r="K7" s="17" t="inlineStr">
         <is>
           <t>Circle,1,0,0,0,0,0</t>
         </is>
       </c>
-      <c r="K7" s="15" t="inlineStr">
+      <c r="L7" s="17" t="inlineStr">
         <is>
           <t>Damage,3001,8000</t>
         </is>
@@ -1185,296 +1245,296 @@
   <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="7.7734375" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="9.1" customWidth="1" style="8" min="1" max="3"/>
-    <col width="10.92" customWidth="1" style="8" min="4" max="4"/>
-    <col width="9.1" customWidth="1" style="8" min="5" max="5"/>
-    <col width="20.01" customWidth="1" style="8" min="6" max="6"/>
-    <col width="9.1" customWidth="1" style="8" min="7" max="7"/>
-    <col width="38.21" customWidth="1" style="8" min="8" max="8"/>
-    <col width="29.11" customWidth="1" style="8" min="9" max="11"/>
+    <col width="9.1" customWidth="1" style="10" min="1" max="3"/>
+    <col width="10.92" customWidth="1" style="10" min="4" max="4"/>
+    <col width="9.1" customWidth="1" style="10" min="5" max="5"/>
+    <col width="20.01" customWidth="1" style="10" min="6" max="6"/>
+    <col width="9.1" customWidth="1" style="10" min="7" max="7"/>
+    <col width="38.21" customWidth="1" style="10" min="8" max="8"/>
+    <col width="29.11" customWidth="1" style="10" min="9" max="11"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="9">
-      <c r="A1" s="10" t="inlineStr">
+    <row r="1" ht="15" customHeight="1" s="11">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>##var</t>
         </is>
       </c>
-      <c r="B1" s="10" t="inlineStr">
+      <c r="B1" s="12" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="C1" s="10" t="inlineStr">
+      <c r="C1" s="12" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="D1" s="10" t="inlineStr">
+      <c r="D1" s="12" t="inlineStr">
         <is>
           <t>durationMs</t>
         </is>
       </c>
-      <c r="E1" s="10" t="inlineStr">
+      <c r="E1" s="12" t="inlineStr">
         <is>
           <t>maxStack</t>
         </is>
       </c>
-      <c r="F1" s="10" t="inlineStr">
+      <c r="F1" s="12" t="inlineStr">
         <is>
           <t>stackMode</t>
         </is>
       </c>
-      <c r="G1" s="10" t="inlineStr">
+      <c r="G1" s="12" t="inlineStr">
         <is>
           <t>tickMs</t>
         </is>
       </c>
-      <c r="H1" s="10" t="inlineStr">
+      <c r="H1" s="12" t="inlineStr">
         <is>
           <t>attrs</t>
         </is>
       </c>
-      <c r="I1" s="10" t="inlineStr">
+      <c r="I1" s="12" t="inlineStr">
         <is>
           <t>tickEffects</t>
         </is>
       </c>
-      <c r="J1" s="10" t="inlineStr">
+      <c r="J1" s="12" t="inlineStr">
         <is>
           <t>beginEffects</t>
         </is>
       </c>
-      <c r="K1" s="10" t="inlineStr">
+      <c r="K1" s="12" t="inlineStr">
         <is>
           <t>endEffects</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1" s="9">
-      <c r="A2" s="11" t="inlineStr">
+    <row r="2" ht="15" customHeight="1" s="11">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>##type</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="C2" s="11" t="inlineStr">
+      <c r="C2" s="13" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="D2" s="11" t="inlineStr">
+      <c r="D2" s="13" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="E2" s="11" t="inlineStr">
+      <c r="E2" s="13" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F2" s="11" t="inlineStr">
+      <c r="F2" s="13" t="inlineStr">
         <is>
           <t>Battle.BuffStackMode</t>
         </is>
       </c>
-      <c r="G2" s="11" t="inlineStr">
+      <c r="G2" s="13" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="H2" s="11" t="inlineStr">
+      <c r="H2" s="13" t="inlineStr">
         <is>
           <t>(array#sep=|),(Attr.AttributePair#sep=,)</t>
         </is>
       </c>
-      <c r="I2" s="11" t="inlineStr">
+      <c r="I2" s="13" t="inlineStr">
         <is>
           <t>(array#sep=|),Battle.EffectRef</t>
         </is>
       </c>
-      <c r="J2" s="11" t="inlineStr">
+      <c r="J2" s="13" t="inlineStr">
         <is>
           <t>(array#sep=|),Battle.EffectRef</t>
         </is>
       </c>
-      <c r="K2" s="11" t="inlineStr">
+      <c r="K2" s="13" t="inlineStr">
         <is>
           <t>(array#sep=|),Battle.EffectRef</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1" s="9">
-      <c r="A3" s="12" t="inlineStr">
+    <row r="3" ht="15" customHeight="1" s="11">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>##group</t>
         </is>
       </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="C3" s="12" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="D3" s="12" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="E3" s="12" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="F3" s="12" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="G3" s="12" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="H3" s="12" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="I3" s="12" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="J3" s="12" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="K3" s="12" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1" s="9">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="C3" s="14" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="D3" s="14" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="E3" s="14" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="F3" s="14" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="G3" s="14" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="H3" s="14" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="I3" s="14" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="J3" s="14" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="K3" s="14" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1" s="11">
+      <c r="A4" s="15" t="inlineStr">
         <is>
           <t>##</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="15" t="inlineStr">
         <is>
           <t>BuffId</t>
         </is>
       </c>
-      <c r="C4" s="13" t="inlineStr">
+      <c r="C4" s="15" t="inlineStr">
         <is>
           <t>Buff名</t>
         </is>
       </c>
-      <c r="D4" s="14" t="inlineStr">
+      <c r="D4" s="16" t="inlineStr">
         <is>
           <t>持续毫秒</t>
         </is>
       </c>
-      <c r="E4" s="14" t="inlineStr">
+      <c r="E4" s="16" t="inlineStr">
         <is>
           <t>最大层数</t>
         </is>
       </c>
-      <c r="F4" s="14" t="inlineStr">
+      <c r="F4" s="16" t="inlineStr">
         <is>
           <t>叠加规则</t>
         </is>
       </c>
-      <c r="G4" s="14" t="inlineStr">
+      <c r="G4" s="16" t="inlineStr">
         <is>
           <t>周期毫秒</t>
         </is>
       </c>
-      <c r="H4" s="14" t="inlineStr">
+      <c r="H4" s="16" t="inlineStr">
         <is>
           <t>属性修改</t>
         </is>
       </c>
-      <c r="I4" s="14" t="inlineStr">
+      <c r="I4" s="16" t="inlineStr">
         <is>
           <t>周期效果</t>
         </is>
       </c>
-      <c r="J4" s="14" t="inlineStr">
+      <c r="J4" s="16" t="inlineStr">
         <is>
           <t>开始效果</t>
         </is>
       </c>
-      <c r="K4" s="14" t="inlineStr">
+      <c r="K4" s="16" t="inlineStr">
         <is>
           <t>结束效果</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="9">
-      <c r="B5" s="8" t="n">
+    <row r="5" ht="15" customHeight="1" s="11">
+      <c r="B5" s="10" t="n">
         <v>7001</v>
       </c>
-      <c r="C5" s="8" t="inlineStr">
+      <c r="C5" s="10" t="inlineStr">
         <is>
           <t>燃烧</t>
         </is>
       </c>
-      <c r="D5" s="8" t="n">
+      <c r="D5" s="10" t="n">
         <v>5000</v>
       </c>
-      <c r="E5" s="8" t="n">
+      <c r="E5" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="F5" s="15" t="inlineStr">
+      <c r="F5" s="17" t="inlineStr">
         <is>
           <t>RefreshAndStack</t>
         </is>
       </c>
-      <c r="G5" s="8" t="n">
+      <c r="G5" s="10" t="n">
         <v>1000</v>
       </c>
-      <c r="I5" s="15" t="inlineStr">
+      <c r="I5" s="17" t="inlineStr">
         <is>
           <t>Damage,3003,10000</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="9">
-      <c r="B6" s="8" t="n">
+    <row r="6" ht="15" customHeight="1" s="11">
+      <c r="B6" s="10" t="n">
         <v>7002</v>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="10" t="inlineStr">
         <is>
           <t>加速</t>
         </is>
       </c>
-      <c r="D6" s="8" t="n">
+      <c r="D6" s="10" t="n">
         <v>3000</v>
       </c>
-      <c r="E6" s="8" t="n">
+      <c r="E6" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="F6" s="15" t="inlineStr">
+      <c r="F6" s="17" t="inlineStr">
         <is>
           <t>Refresh</t>
         </is>
       </c>
-      <c r="G6" s="8" t="n">
+      <c r="G6" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="H6" s="15" t="inlineStr">
+      <c r="H6" s="17" t="inlineStr">
         <is>
           <t>104,500</t>
         </is>
@@ -1497,112 +1557,109 @@
   <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="7.7734375" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="10" customWidth="1" style="8" min="1" max="3"/>
-    <col width="10" customWidth="1" style="9" min="2" max="2"/>
-    <col width="10" customWidth="1" style="9" min="3" max="3"/>
-    <col width="20" customWidth="1" style="8" min="4" max="4"/>
-    <col width="10" customWidth="1" style="8" min="5" max="5"/>
-    <col width="12" customWidth="1" style="8" min="6" max="6"/>
-    <col width="15" customWidth="1" style="8" min="7" max="7"/>
-    <col width="10" customWidth="1" style="8" min="8" max="9"/>
-    <col width="10" customWidth="1" style="9" min="9" max="9"/>
-    <col width="17" customWidth="1" style="9" min="10" max="10"/>
+    <col width="10" customWidth="1" style="10" min="1" max="3"/>
+    <col width="20" customWidth="1" style="10" min="4" max="4"/>
+    <col width="10" customWidth="1" style="10" min="5" max="5"/>
+    <col width="12" customWidth="1" style="10" min="6" max="6"/>
+    <col width="15" customWidth="1" style="10" min="7" max="7"/>
+    <col width="10" customWidth="1" style="10" min="8" max="9"/>
+    <col width="17" customWidth="1" style="10" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="9">
-      <c r="A1" s="16" t="inlineStr">
+    <row r="1" ht="15" customHeight="1" s="11">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>##var</t>
         </is>
       </c>
-      <c r="B1" s="16" t="inlineStr">
+      <c r="B1" s="12" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="C1" s="16" t="inlineStr">
+      <c r="C1" s="12" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="D1" s="16" t="inlineStr">
+      <c r="D1" s="12" t="inlineStr">
         <is>
           <t>attr</t>
         </is>
       </c>
-      <c r="E1" s="16" t="inlineStr">
+      <c r="E1" s="12" t="inlineStr">
         <is>
           <t>ratio</t>
         </is>
       </c>
-      <c r="F1" s="16" t="inlineStr">
+      <c r="F1" s="12" t="inlineStr">
         <is>
           <t>fixedValue</t>
         </is>
       </c>
-      <c r="G1" s="16" t="inlineStr">
+      <c r="G1" s="12" t="inlineStr">
         <is>
           <t>damageElement</t>
         </is>
       </c>
-      <c r="H1" s="16" t="inlineStr">
+      <c r="H1" s="12" t="inlineStr">
         <is>
           <t>canCrit</t>
         </is>
       </c>
-      <c r="I1" s="16" t="inlineStr">
+      <c r="I1" s="12" t="inlineStr">
         <is>
           <t>hitCount</t>
         </is>
       </c>
-      <c r="J1" s="16" t="inlineStr">
+      <c r="J1" s="12" t="inlineStr">
         <is>
           <t>playHitReaction</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1" s="9">
-      <c r="A2" s="17" t="inlineStr">
+    <row r="2" ht="15" customHeight="1" s="11">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>##type</t>
         </is>
       </c>
-      <c r="B2" s="17" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="C2" s="17" t="inlineStr">
+      <c r="C2" s="13" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="D2" s="17" t="inlineStr">
+      <c r="D2" s="13" t="inlineStr">
         <is>
           <t>Attr.AttributeType</t>
         </is>
       </c>
-      <c r="E2" s="17" t="inlineStr">
+      <c r="E2" s="13" t="inlineStr">
         <is>
           <t>long</t>
         </is>
       </c>
-      <c r="F2" s="17" t="inlineStr">
+      <c r="F2" s="13" t="inlineStr">
         <is>
           <t>long</t>
         </is>
       </c>
-      <c r="G2" s="17" t="inlineStr">
+      <c r="G2" s="13" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="H2" s="17" t="inlineStr">
+      <c r="H2" s="13" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="I2" s="17" t="inlineStr">
+      <c r="I2" s="13" t="inlineStr">
         <is>
           <t>int</t>
         </is>
@@ -1613,207 +1670,213 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1" s="9">
-      <c r="A3" s="19" t="inlineStr">
+    <row r="3" ht="15" customHeight="1" s="11">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>##group</t>
         </is>
       </c>
-      <c r="B3" s="19" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="C3" s="19" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="D3" s="19" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="E3" s="19" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="F3" s="19" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="G3" s="19" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="H3" s="19" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="I3" s="19" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="J3" s="20" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1" s="9">
-      <c r="A4" s="21" t="inlineStr">
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="C3" s="14" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="D3" s="14" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="E3" s="14" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="F3" s="14" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="G3" s="14" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="H3" s="14" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="I3" s="14" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="J3" s="19" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1" s="11">
+      <c r="A4" s="15" t="inlineStr">
         <is>
           <t>##</t>
         </is>
       </c>
-      <c r="B4" s="22" t="inlineStr">
+      <c r="B4" s="16" t="inlineStr">
         <is>
           <t>效果id</t>
         </is>
       </c>
-      <c r="C4" s="22" t="inlineStr">
+      <c r="C4" s="16" t="inlineStr">
         <is>
           <t>效果名</t>
         </is>
       </c>
-      <c r="D4" s="22" t="inlineStr">
+      <c r="D4" s="16" t="inlineStr">
         <is>
           <t>取值属性</t>
         </is>
       </c>
-      <c r="E4" s="22" t="inlineStr">
+      <c r="E4" s="16" t="inlineStr">
         <is>
           <t>属性倍率</t>
         </is>
       </c>
-      <c r="F4" s="22" t="inlineStr">
+      <c r="F4" s="16" t="inlineStr">
         <is>
           <t>固定伤害</t>
         </is>
       </c>
-      <c r="G4" s="22" t="inlineStr">
+      <c r="G4" s="16" t="inlineStr">
         <is>
           <t>伤害元素</t>
         </is>
       </c>
-      <c r="H4" s="22" t="inlineStr">
+      <c r="H4" s="16" t="inlineStr">
         <is>
           <t>是否暴击</t>
         </is>
       </c>
-      <c r="I4" s="22" t="inlineStr">
+      <c r="I4" s="16" t="inlineStr">
         <is>
           <t>最大命中数</t>
         </is>
       </c>
-      <c r="J4" s="22" t="inlineStr">
+      <c r="J4" s="16" t="inlineStr">
         <is>
           <t>是否播放受击</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="9">
-      <c r="B5" s="8" t="n">
+    <row r="5" ht="15" customHeight="1" s="11">
+      <c r="B5" s="10" t="n">
         <v>3001</v>
       </c>
-      <c r="C5" s="8" t="inlineStr">
+      <c r="C5" s="10" t="inlineStr">
         <is>
           <t>普攻伤害</t>
         </is>
       </c>
-      <c r="D5" s="15" t="inlineStr">
+      <c r="D5" s="17" t="inlineStr">
         <is>
           <t>Atk</t>
         </is>
       </c>
-      <c r="E5" s="8" t="n">
+      <c r="E5" s="10" t="n">
         <v>10000</v>
       </c>
-      <c r="F5" s="8" t="n">
+      <c r="F5" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="G5" s="8" t="n">
+      <c r="G5" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="H5" s="15" t="b">
+      <c r="H5" s="17">
+        <f>TRUE()</f>
+        <v/>
+      </c>
+      <c r="I5" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="I5" s="8" t="n">
+      <c r="J5" s="10">
+        <f>TRUE()</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1" s="11">
+      <c r="B6" s="10" t="n">
+        <v>3002</v>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>火球命中伤害</t>
+        </is>
+      </c>
+      <c r="D6" s="17" t="inlineStr">
+        <is>
+          <t>Atk</t>
+        </is>
+      </c>
+      <c r="E6" s="10" t="n">
+        <v>12000</v>
+      </c>
+      <c r="F6" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="17">
+        <f>TRUE()</f>
+        <v/>
+      </c>
+      <c r="I6" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J5" s="8" t="b">
+      <c r="J6" s="10">
+        <f>TRUE()</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1" s="11">
+      <c r="B7" s="10" t="n">
+        <v>3003</v>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>燃烧周期伤害</t>
+        </is>
+      </c>
+      <c r="D7" s="17" t="inlineStr">
+        <is>
+          <t>Atk</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="n">
+        <v>3000</v>
+      </c>
+      <c r="F7" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="10" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" ht="15" customHeight="1" s="9">
-      <c r="B6" s="8" t="n">
-        <v>3002</v>
-      </c>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>火球命中伤害</t>
-        </is>
-      </c>
-      <c r="D6" s="15" t="inlineStr">
-        <is>
-          <t>Atk</t>
-        </is>
-      </c>
-      <c r="E6" s="8" t="n">
-        <v>12000</v>
-      </c>
-      <c r="F6" s="8" t="n">
+      <c r="H7" s="17">
+        <f>FALSE()</f>
+        <v/>
+      </c>
+      <c r="I7" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="G6" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="I6" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="J6" s="8" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1" s="9">
-      <c r="B7" s="8" t="n">
-        <v>3003</v>
-      </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>燃烧周期伤害</t>
-        </is>
-      </c>
-      <c r="D7" s="15" t="inlineStr">
-        <is>
-          <t>Atk</t>
-        </is>
-      </c>
-      <c r="E7" s="8" t="n">
-        <v>3000</v>
-      </c>
-      <c r="F7" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" s="15" t="b">
-        <v>0</v>
-      </c>
-      <c r="I7" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="8" t="b">
-        <v>0</v>
+      <c r="J7" s="10">
+        <f>FALSE()</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -1833,207 +1896,207 @@
   <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="7.7734375" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="9.1" customWidth="1" style="8" min="1" max="3"/>
-    <col width="18.2" customWidth="1" style="8" min="4" max="4"/>
-    <col width="9.1" customWidth="1" style="8" min="5" max="5"/>
-    <col width="10.92" customWidth="1" style="8" min="6" max="6"/>
-    <col width="9.1" customWidth="1" style="8" min="7" max="7"/>
+    <col width="9.1" customWidth="1" style="10" min="1" max="3"/>
+    <col width="18.2" customWidth="1" style="10" min="4" max="4"/>
+    <col width="9.1" customWidth="1" style="10" min="5" max="5"/>
+    <col width="10.92" customWidth="1" style="10" min="6" max="6"/>
+    <col width="9.1" customWidth="1" style="10" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="9">
-      <c r="A1" s="10" t="inlineStr">
+    <row r="1" ht="15" customHeight="1" s="11">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>##var</t>
         </is>
       </c>
-      <c r="B1" s="10" t="inlineStr">
+      <c r="B1" s="12" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="C1" s="10" t="inlineStr">
+      <c r="C1" s="12" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="D1" s="10" t="inlineStr">
+      <c r="D1" s="12" t="inlineStr">
         <is>
           <t>attr</t>
         </is>
       </c>
-      <c r="E1" s="10" t="inlineStr">
+      <c r="E1" s="12" t="inlineStr">
         <is>
           <t>ratio</t>
         </is>
       </c>
-      <c r="F1" s="10" t="inlineStr">
+      <c r="F1" s="12" t="inlineStr">
         <is>
           <t>fixedValue</t>
         </is>
       </c>
-      <c r="G1" s="10" t="inlineStr">
+      <c r="G1" s="12" t="inlineStr">
         <is>
           <t>canCrit</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1" s="9">
-      <c r="A2" s="11" t="inlineStr">
+    <row r="2" ht="15" customHeight="1" s="11">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>##type</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="C2" s="11" t="inlineStr">
+      <c r="C2" s="13" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="D2" s="11" t="inlineStr">
+      <c r="D2" s="13" t="inlineStr">
         <is>
           <t>Attr.AttributeType</t>
         </is>
       </c>
-      <c r="E2" s="11" t="inlineStr">
+      <c r="E2" s="13" t="inlineStr">
         <is>
           <t>long</t>
         </is>
       </c>
-      <c r="F2" s="11" t="inlineStr">
+      <c r="F2" s="13" t="inlineStr">
         <is>
           <t>long</t>
         </is>
       </c>
-      <c r="G2" s="11" t="inlineStr">
+      <c r="G2" s="13" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1" s="9">
-      <c r="A3" s="12" t="inlineStr">
+    <row r="3" ht="15" customHeight="1" s="11">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>##group</t>
         </is>
       </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="C3" s="12" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="D3" s="12" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="E3" s="12" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="F3" s="12" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="G3" s="12" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1" s="9">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="C3" s="14" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="D3" s="14" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="E3" s="14" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="F3" s="14" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="G3" s="14" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1" s="11">
+      <c r="A4" s="15" t="inlineStr">
         <is>
           <t>##</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B4" s="16" t="inlineStr">
         <is>
           <t>效果id</t>
         </is>
       </c>
-      <c r="C4" s="14" t="inlineStr">
+      <c r="C4" s="16" t="inlineStr">
         <is>
           <t>效果名</t>
         </is>
       </c>
-      <c r="D4" s="14" t="inlineStr">
+      <c r="D4" s="16" t="inlineStr">
         <is>
           <t>取值属性</t>
         </is>
       </c>
-      <c r="E4" s="14" t="inlineStr">
+      <c r="E4" s="16" t="inlineStr">
         <is>
           <t>属性倍率</t>
         </is>
       </c>
-      <c r="F4" s="14" t="inlineStr">
+      <c r="F4" s="16" t="inlineStr">
         <is>
           <t>固定回血</t>
         </is>
       </c>
-      <c r="G4" s="14" t="inlineStr">
+      <c r="G4" s="16" t="inlineStr">
         <is>
           <t>是否暴击</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="9">
-      <c r="B5" s="8" t="n">
+    <row r="5" ht="15" customHeight="1" s="11">
+      <c r="B5" s="10" t="n">
         <v>4001</v>
       </c>
-      <c r="C5" s="8" t="inlineStr">
+      <c r="C5" s="10" t="inlineStr">
         <is>
           <t>小治疗</t>
         </is>
       </c>
-      <c r="D5" s="15" t="inlineStr">
+      <c r="D5" s="17" t="inlineStr">
         <is>
           <t>HpMax</t>
         </is>
       </c>
-      <c r="E5" s="8" t="n">
+      <c r="E5" s="10" t="n">
         <v>1000</v>
       </c>
-      <c r="F5" s="8" t="n">
+      <c r="F5" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="G5" s="15">
+      <c r="G5" s="17">
         <f>FALSE()</f>
         <v/>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="9">
-      <c r="B6" s="8" t="n">
+    <row r="6" ht="15" customHeight="1" s="11">
+      <c r="B6" s="10" t="n">
         <v>4002</v>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="10" t="inlineStr">
         <is>
           <t>固定回血</t>
         </is>
       </c>
-      <c r="D6" s="15" t="inlineStr">
+      <c r="D6" s="17" t="inlineStr">
         <is>
           <t>Null</t>
         </is>
       </c>
-      <c r="E6" s="8" t="n">
+      <c r="E6" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="F6" s="8" t="n">
+      <c r="F6" s="10" t="n">
         <v>50</v>
       </c>
-      <c r="G6" s="15">
+      <c r="G6" s="17">
         <f>FALSE()</f>
         <v/>
       </c>
@@ -2055,174 +2118,174 @@
   <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="7.7734375" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="9.1" customWidth="1" style="8" min="1" max="4"/>
-    <col width="18.2" customWidth="1" style="8" min="5" max="5"/>
-    <col width="9.1" customWidth="1" style="8" min="6" max="6"/>
+    <col width="9.1" customWidth="1" style="10" min="1" max="4"/>
+    <col width="18.2" customWidth="1" style="10" min="5" max="5"/>
+    <col width="9.1" customWidth="1" style="10" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="9">
-      <c r="A1" s="10" t="inlineStr">
+    <row r="1" ht="15" customHeight="1" s="11">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>##var</t>
         </is>
       </c>
-      <c r="B1" s="10" t="inlineStr">
+      <c r="B1" s="12" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="C1" s="10" t="inlineStr">
+      <c r="C1" s="12" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="D1" s="10" t="inlineStr">
+      <c r="D1" s="12" t="inlineStr">
         <is>
           <t>buffId</t>
         </is>
       </c>
-      <c r="E1" s="10" t="inlineStr">
+      <c r="E1" s="12" t="inlineStr">
         <is>
           <t>durationOverrideMs</t>
         </is>
       </c>
-      <c r="F1" s="10" t="inlineStr">
+      <c r="F1" s="12" t="inlineStr">
         <is>
           <t>stack</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1" s="9">
-      <c r="A2" s="11" t="inlineStr">
+    <row r="2" ht="15" customHeight="1" s="11">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>##type</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="C2" s="11" t="inlineStr">
+      <c r="C2" s="13" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="D2" s="11" t="inlineStr">
+      <c r="D2" s="13" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="E2" s="11" t="inlineStr">
+      <c r="E2" s="13" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F2" s="11" t="inlineStr">
+      <c r="F2" s="13" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1" s="9">
-      <c r="A3" s="12" t="inlineStr">
+    <row r="3" ht="15" customHeight="1" s="11">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>##group</t>
         </is>
       </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="C3" s="12" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="D3" s="12" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="E3" s="12" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="F3" s="12" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1" s="9">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="C3" s="14" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="D3" s="14" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="E3" s="14" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="F3" s="14" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1" s="11">
+      <c r="A4" s="15" t="inlineStr">
         <is>
           <t>##</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B4" s="16" t="inlineStr">
         <is>
           <t>效果id</t>
         </is>
       </c>
-      <c r="C4" s="14" t="inlineStr">
+      <c r="C4" s="16" t="inlineStr">
         <is>
           <t>效果名</t>
         </is>
       </c>
-      <c r="D4" s="13" t="inlineStr">
+      <c r="D4" s="15" t="inlineStr">
         <is>
           <t>BuffId</t>
         </is>
       </c>
-      <c r="E4" s="14" t="inlineStr">
+      <c r="E4" s="16" t="inlineStr">
         <is>
           <t>覆盖持续时间毫秒</t>
         </is>
       </c>
-      <c r="F4" s="14" t="inlineStr">
+      <c r="F4" s="16" t="inlineStr">
         <is>
           <t>增加层数</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="9">
-      <c r="B5" s="8" t="n">
+    <row r="5" ht="15" customHeight="1" s="11">
+      <c r="B5" s="10" t="n">
         <v>5001</v>
       </c>
-      <c r="C5" s="8" t="inlineStr">
+      <c r="C5" s="10" t="inlineStr">
         <is>
           <t>添加燃烧</t>
         </is>
       </c>
-      <c r="D5" s="8" t="n">
+      <c r="D5" s="10" t="n">
         <v>7001</v>
       </c>
-      <c r="E5" s="8" t="n">
+      <c r="E5" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="F5" s="8" t="n">
+      <c r="F5" s="10" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="9">
-      <c r="B6" s="8" t="n">
+    <row r="6" ht="15" customHeight="1" s="11">
+      <c r="B6" s="10" t="n">
         <v>5002</v>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="10" t="inlineStr">
         <is>
           <t>添加加速</t>
         </is>
       </c>
-      <c r="D6" s="8" t="n">
+      <c r="D6" s="10" t="n">
         <v>7002</v>
       </c>
-      <c r="E6" s="8" t="n">
+      <c r="E6" s="10" t="n">
         <v>3000</v>
       </c>
-      <c r="F6" s="8" t="n">
+      <c r="F6" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2240,256 +2303,321 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="7.7734375" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="9.1" customWidth="1" style="8" min="1" max="3"/>
-    <col width="19.11" customWidth="1" style="8" min="4" max="4"/>
-    <col width="9.1" customWidth="1" style="8" min="5" max="6"/>
-    <col width="10.92" customWidth="1" style="8" min="7" max="7"/>
-    <col width="11.83" customWidth="1" style="8" min="8" max="8"/>
-    <col width="13.65" customWidth="1" style="8" min="9" max="9"/>
-    <col width="30.93" customWidth="1" style="8" min="10" max="10"/>
+    <col width="9.1" customWidth="1" style="10" min="1" max="3"/>
+    <col width="19.11" customWidth="1" style="10" min="4" max="4"/>
+    <col width="9.1" customWidth="1" style="10" min="5" max="6"/>
+    <col width="10.92" customWidth="1" style="10" min="7" max="7"/>
+    <col width="11.83" customWidth="1" style="10" min="8" max="8"/>
+    <col width="13.65" customWidth="1" style="10" min="9" max="9"/>
+    <col width="30.93" customWidth="1" style="10" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="9">
-      <c r="A1" s="10" t="inlineStr">
+    <row r="1" ht="15" customHeight="1" s="11">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>##var</t>
         </is>
       </c>
-      <c r="B1" s="10" t="inlineStr">
+      <c r="B1" s="12" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="C1" s="10" t="inlineStr">
+      <c r="C1" s="12" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="D1" s="10" t="inlineStr">
+      <c r="D1" s="12" t="inlineStr">
         <is>
           <t>projectileKey</t>
         </is>
       </c>
-      <c r="E1" s="10" t="inlineStr">
+      <c r="E1" s="12" t="inlineStr">
         <is>
           <t>speed</t>
         </is>
       </c>
-      <c r="F1" s="10" t="inlineStr">
+      <c r="F1" s="12" t="inlineStr">
         <is>
           <t>radius</t>
         </is>
       </c>
-      <c r="G1" s="10" t="inlineStr">
+      <c r="G1" s="12" t="inlineStr">
         <is>
           <t>lifetimeMs</t>
         </is>
       </c>
-      <c r="H1" s="10" t="inlineStr">
+      <c r="H1" s="12" t="inlineStr">
         <is>
           <t>pierceCount</t>
         </is>
       </c>
-      <c r="I1" s="10" t="inlineStr">
+      <c r="I1" s="12" t="inlineStr">
         <is>
           <t>hitIntervalMs</t>
         </is>
       </c>
-      <c r="J1" s="10" t="inlineStr">
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>queryQuality</t>
+        </is>
+      </c>
+      <c r="K1" s="12" t="inlineStr">
         <is>
           <t>hitEffects</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1" s="9">
-      <c r="A2" s="11" t="inlineStr">
+    <row r="2" ht="15" customHeight="1" s="11">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>##type</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="C2" s="11" t="inlineStr">
+      <c r="C2" s="13" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="D2" s="11" t="inlineStr">
+      <c r="D2" s="13" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="E2" s="11" t="inlineStr">
+      <c r="E2" s="13" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="F2" s="11" t="inlineStr">
+      <c r="F2" s="13" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="G2" s="11" t="inlineStr">
+      <c r="G2" s="13" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="H2" s="11" t="inlineStr">
+      <c r="H2" s="13" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="I2" s="11" t="inlineStr">
+      <c r="I2" s="13" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="J2" s="11" t="inlineStr">
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Battle.QueryQuality</t>
+        </is>
+      </c>
+      <c r="K2" s="13" t="inlineStr">
         <is>
           <t>(array#sep=|),Battle.EffectRef</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1" s="9">
-      <c r="A3" s="12" t="inlineStr">
+    <row r="3" ht="15" customHeight="1" s="11">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>##group</t>
         </is>
       </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="C3" s="12" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="D3" s="12" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="E3" s="12" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="F3" s="12" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="G3" s="12" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="H3" s="12" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="I3" s="12" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="J3" s="12" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1" s="9">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="C3" s="14" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="D3" s="14" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="E3" s="14" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="F3" s="14" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="G3" s="14" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="H3" s="14" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="I3" s="14" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="K3" s="14" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1" s="11">
+      <c r="A4" s="15" t="inlineStr">
         <is>
           <t>##</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B4" s="16" t="inlineStr">
         <is>
           <t>效果id</t>
         </is>
       </c>
-      <c r="C4" s="14" t="inlineStr">
+      <c r="C4" s="16" t="inlineStr">
         <is>
           <t>效果名</t>
         </is>
       </c>
-      <c r="D4" s="14" t="inlineStr">
+      <c r="D4" s="16" t="inlineStr">
         <is>
           <t>抛射物表现key</t>
         </is>
       </c>
-      <c r="E4" s="14" t="inlineStr">
+      <c r="E4" s="16" t="inlineStr">
         <is>
           <t>速度</t>
         </is>
       </c>
-      <c r="F4" s="14" t="inlineStr">
+      <c r="F4" s="16" t="inlineStr">
         <is>
           <t>碰撞半径</t>
         </is>
       </c>
-      <c r="G4" s="14" t="inlineStr">
+      <c r="G4" s="16" t="inlineStr">
         <is>
           <t>存活毫秒</t>
         </is>
       </c>
-      <c r="H4" s="14" t="inlineStr">
+      <c r="H4" s="16" t="inlineStr">
         <is>
           <t>穿透次数</t>
         </is>
       </c>
-      <c r="I4" s="14" t="inlineStr">
+      <c r="I4" s="16" t="inlineStr">
         <is>
           <t>同目标命中间隔</t>
         </is>
       </c>
-      <c r="J4" s="14" t="inlineStr">
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>????</t>
+        </is>
+      </c>
+      <c r="K4" s="16" t="inlineStr">
         <is>
           <t>命中效果</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="9">
-      <c r="B5" s="8" t="n">
+    <row r="5" ht="15" customHeight="1" s="11">
+      <c r="B5" s="10" t="n">
         <v>6001</v>
       </c>
-      <c r="C5" s="8" t="inlineStr">
-        <is>
-          <t>火球</t>
-        </is>
-      </c>
-      <c r="D5" s="15" t="inlineStr">
-        <is>
-          <t>projectile_fireball</t>
-        </is>
-      </c>
-      <c r="E5" s="8" t="n">
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>远程普攻</t>
+        </is>
+      </c>
+      <c r="D5" s="17" t="inlineStr">
+        <is>
+          <t>FA_Consumable_Arrow_008_Blue_Atlas</t>
+        </is>
+      </c>
+      <c r="E5" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="F5" s="8" t="n">
+      <c r="F5" s="10" t="n">
         <v>0.25</v>
       </c>
-      <c r="G5" s="8" t="n">
+      <c r="G5" s="10" t="n">
         <v>3000</v>
       </c>
-      <c r="H5" s="8" t="n">
+      <c r="H5" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="I5" s="8" t="n">
+      <c r="I5" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="J5" s="15" t="inlineStr">
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K5" s="17" t="inlineStr">
+        <is>
+          <t>Damage,3002,10000</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1" s="11">
+      <c r="B6" s="10" t="n">
+        <v>6002</v>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>远程普攻</t>
+        </is>
+      </c>
+      <c r="D6" s="17" t="inlineStr">
+        <is>
+          <t>projectile_arrow</t>
+        </is>
+      </c>
+      <c r="E6" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="F6" s="10" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G6" s="10" t="n">
+        <v>3000</v>
+      </c>
+      <c r="H6" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K6" s="17" t="inlineStr">
         <is>
           <t>Damage,3002,10000|AddBuff,5001,0</t>
         </is>

--- a/Excels/Excels/B-Battle_战斗表.xlsx
+++ b/Excels/Excels/B-Battle_战斗表.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="Unit" sheetId="1" state="visible" r:id="rId3"/>
@@ -507,7 +507,7 @@
     <t xml:space="preserve">同目标命中间隔</t>
   </si>
   <si>
-    <t xml:space="preserve">????</t>
+    <t xml:space="preserve">碰撞检测质量</t>
   </si>
   <si>
     <t xml:space="preserve">命中效果</t>
@@ -516,7 +516,7 @@
     <t xml:space="preserve">FA_Consumable_Arrow_008_Blue_Atlas</t>
   </si>
   <si>
-    <t xml:space="preserve">High</t>
+    <t xml:space="preserve">Low</t>
   </si>
   <si>
     <t xml:space="preserve">Damage,3002,10000</t>
@@ -2496,7 +2496,7 @@
         <v>8</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>0.25</v>
+        <v>0.1</v>
       </c>
       <c r="G5" s="1" t="n">
         <v>3000</v>

--- a/Excels/Excels/B-Battle_战斗表.xlsx
+++ b/Excels/Excels/B-Battle_战斗表.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="6"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Unit" sheetId="1" state="visible" r:id="rId3"/>
@@ -118,7 +118,7 @@
     <t xml:space="preserve">弓箭手</t>
   </si>
   <si>
-    <t xml:space="preserve">102,500|105,500|101,50|103,10|104,300|201,1</t>
+    <t xml:space="preserve">102,500|105,500|101,50|103,10|104,300</t>
   </si>
   <si>
     <t xml:space="preserve">Character_1_AnimationVit</t>
@@ -127,26 +127,7 @@
     <t xml:space="preserve">野蛮人</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">102,1000|105,1000|101,50|103,10|104,300</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">|201,1</t>
-    </r>
+    <t xml:space="preserve">102,1000|105,1000|101,50|103,10|104,300</t>
   </si>
   <si>
     <t xml:space="preserve">Character_2_AnimationVit</t>
@@ -251,7 +232,7 @@
     <t xml:space="preserve">Nearest</t>
   </si>
   <si>
-    <t xml:space="preserve">Circle,1.2,0,0,0,0,0</t>
+    <t xml:space="preserve">Null,1.2,0,0,0,0,0</t>
   </si>
   <si>
     <t xml:space="preserve">Damage,3001,10000</t>
@@ -535,7 +516,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -574,13 +555,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="134"/>
     </font>
   </fonts>
   <fills count="6">
@@ -1458,7 +1432,7 @@
         <v>1000</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="I5" s="7" t="s">
         <v>63</v>

--- a/Excels/Excels/B-Battle_战斗表.xlsx
+++ b/Excels/Excels/B-Battle_战斗表.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Unit" sheetId="1" state="visible" r:id="rId3"/>
@@ -1467,7 +1467,7 @@
         <v>2000</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I6" s="7" t="s">
         <v>63</v>

--- a/Excels/Excels/B-Battle_战斗表.xlsx
+++ b/Excels/Excels/B-Battle_战斗表.xlsx
@@ -3214,11 +3214,11 @@
       </c>
       <c r="G7" s="28" t="inlineStr">
         <is>
-          <t>Skill</t>
+          <t>Projectile</t>
         </is>
       </c>
       <c r="H7" s="28" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I7" s="28" t="inlineStr">
         <is>
@@ -3264,11 +3264,11 @@
       </c>
       <c r="G8" s="28" t="inlineStr">
         <is>
-          <t>Skill</t>
+          <t>Projectile</t>
         </is>
       </c>
       <c r="H8" s="28" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I8" s="28" t="inlineStr">
         <is>
@@ -3314,11 +3314,11 @@
       </c>
       <c r="G9" s="28" t="inlineStr">
         <is>
-          <t>Skill</t>
+          <t>Projectile</t>
         </is>
       </c>
       <c r="H9" s="28" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I9" s="28" t="inlineStr">
         <is>

--- a/Excels/Excels/B-Battle_战斗表.xlsx
+++ b/Excels/Excels/B-Battle_战斗表.xlsx
@@ -953,7 +953,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="7.7734375" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="9.1" customWidth="1" style="11" min="1" max="3"/>
@@ -1021,6 +1021,11 @@
           <t>endEffects</t>
         </is>
       </c>
+      <c r="L1" s="11" t="inlineStr">
+        <is>
+          <t>modifiers</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="15" customHeight="1" s="12">
       <c r="A2" s="14" t="inlineStr">
@@ -1078,6 +1083,11 @@
           <t>(array#sep=|),Battle.EffectRef</t>
         </is>
       </c>
+      <c r="L2" s="11" t="inlineStr">
+        <is>
+          <t>(array#sep=|),Battle.BattleModifierRef</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="15" customHeight="1" s="12">
       <c r="A3" s="15" t="inlineStr">
@@ -1135,6 +1145,11 @@
           <t>c</t>
         </is>
       </c>
+      <c r="L3" s="11" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="15" customHeight="1" s="12">
       <c r="A4" s="16" t="inlineStr">
@@ -1190,6 +1205,11 @@
       <c r="K4" s="17" t="inlineStr">
         <is>
           <t>结束效果</t>
+        </is>
+      </c>
+      <c r="L4" s="11" t="inlineStr">
+        <is>
+          <t>????</t>
         </is>
       </c>
     </row>
@@ -1248,6 +1268,39 @@
       <c r="H6" s="18" t="inlineStr">
         <is>
           <t>104,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="11" t="n">
+        <v>7003</v>
+      </c>
+      <c r="C7" s="11" t="inlineStr">
+        <is>
+          <t>???????</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="n">
+        <v>99</v>
+      </c>
+      <c r="E7" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="11" t="inlineStr">
+        <is>
+          <t>Refresh</t>
+        </is>
+      </c>
+      <c r="G7" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="11" t="inlineStr"/>
+      <c r="I7" s="11" t="inlineStr"/>
+      <c r="J7" s="11" t="inlineStr"/>
+      <c r="K7" s="11" t="inlineStr"/>
+      <c r="L7" s="11" t="inlineStr">
+        <is>
+          <t>Skill;1;Int,1;Null,0,0</t>
         </is>
       </c>
     </row>

--- a/Excels/Excels/B-Battle_战斗表.xlsx
+++ b/Excels/Excels/B-Battle_战斗表.xlsx
@@ -2875,7 +2875,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" style="12" min="1" max="1"/>
@@ -2923,32 +2923,37 @@
           <t>skillSelector</t>
         </is>
       </c>
-      <c r="G1" s="21" t="inlineStr">
+      <c r="G1" s="11" t="inlineStr">
+        <is>
+          <t>triggerEventType</t>
+        </is>
+      </c>
+      <c r="H1" s="21" t="inlineStr">
         <is>
           <t>targetType</t>
         </is>
       </c>
-      <c r="H1" s="21" t="inlineStr">
+      <c r="I1" s="21" t="inlineStr">
         <is>
           <t>modifierType</t>
         </is>
       </c>
-      <c r="I1" s="21" t="inlineStr">
+      <c r="J1" s="21" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="J1" s="21" t="inlineStr">
+      <c r="K1" s="21" t="inlineStr">
         <is>
           <t>effect</t>
         </is>
       </c>
-      <c r="K1" s="21" t="inlineStr">
+      <c r="L1" s="21" t="inlineStr">
         <is>
           <t>maxStack</t>
         </is>
       </c>
-      <c r="L1" s="21" t="inlineStr">
+      <c r="M1" s="21" t="inlineStr">
         <is>
           <t>weight</t>
         </is>
@@ -2985,32 +2990,37 @@
           <t>Battle.SkillSelector</t>
         </is>
       </c>
-      <c r="G2" s="23" t="inlineStr">
+      <c r="G2" s="11" t="inlineStr">
+        <is>
+          <t>Battle.TriggerEventType</t>
+        </is>
+      </c>
+      <c r="H2" s="23" t="inlineStr">
         <is>
           <t>Battle.ModifierTargetType</t>
         </is>
       </c>
-      <c r="H2" s="23" t="inlineStr">
+      <c r="I2" s="23" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="I2" s="23" t="inlineStr">
+      <c r="J2" s="23" t="inlineStr">
         <is>
           <t>Battle.ModifierValue</t>
         </is>
       </c>
-      <c r="J2" s="23" t="inlineStr">
+      <c r="K2" s="23" t="inlineStr">
         <is>
           <t>Battle.EffectRef</t>
         </is>
       </c>
-      <c r="K2" s="23" t="inlineStr">
+      <c r="L2" s="23" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="L2" s="23" t="inlineStr">
+      <c r="M2" s="23" t="inlineStr">
         <is>
           <t>int</t>
         </is>
@@ -3047,7 +3057,7 @@
           <t>c</t>
         </is>
       </c>
-      <c r="G3" s="25" t="inlineStr">
+      <c r="G3" s="11" t="inlineStr">
         <is>
           <t>c</t>
         </is>
@@ -3073,6 +3083,11 @@
         </is>
       </c>
       <c r="L3" s="25" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="M3" s="25" t="inlineStr">
         <is>
           <t>c</t>
         </is>
@@ -3109,32 +3124,37 @@
           <t>技能筛选</t>
         </is>
       </c>
-      <c r="G4" s="27" t="inlineStr">
+      <c r="G4" s="11" t="inlineStr">
+        <is>
+          <t>??????</t>
+        </is>
+      </c>
+      <c r="H4" s="27" t="inlineStr">
         <is>
           <t>目标类型</t>
         </is>
       </c>
-      <c r="H4" s="27" t="inlineStr">
+      <c r="I4" s="27" t="inlineStr">
         <is>
           <t>强化类型</t>
         </is>
       </c>
-      <c r="I4" s="27" t="inlineStr">
+      <c r="J4" s="27" t="inlineStr">
         <is>
           <t>数值</t>
         </is>
       </c>
-      <c r="J4" s="27" t="inlineStr">
+      <c r="K4" s="27" t="inlineStr">
         <is>
           <t>效果</t>
         </is>
       </c>
-      <c r="K4" s="27" t="inlineStr">
+      <c r="L4" s="27" t="inlineStr">
         <is>
           <t>最大层数</t>
         </is>
       </c>
-      <c r="L4" s="27" t="inlineStr">
+      <c r="M4" s="27" t="inlineStr">
         <is>
           <t>权重</t>
         </is>
@@ -3165,28 +3185,33 @@
           <t>0,</t>
         </is>
       </c>
-      <c r="G5" s="28" t="inlineStr">
+      <c r="G5" s="11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H5" s="28" t="inlineStr">
         <is>
           <t>Skill</t>
         </is>
       </c>
-      <c r="H5" s="28" t="n">
+      <c r="I5" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="I5" s="28" t="inlineStr">
+      <c r="J5" s="28" t="inlineStr">
         <is>
           <t>Int,1</t>
         </is>
       </c>
-      <c r="J5" s="28" t="inlineStr">
+      <c r="K5" s="28" t="inlineStr">
         <is>
           <t>Null,0,0</t>
         </is>
       </c>
-      <c r="K5" s="28" t="n">
+      <c r="L5" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="L5" s="28" t="n">
+      <c r="M5" s="28" t="n">
         <v>100</v>
       </c>
     </row>
@@ -3215,28 +3240,33 @@
           <t>0,</t>
         </is>
       </c>
-      <c r="G6" s="28" t="inlineStr">
+      <c r="G6" s="11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H6" s="28" t="inlineStr">
         <is>
           <t>Skill</t>
         </is>
       </c>
-      <c r="H6" s="28" t="n">
+      <c r="I6" s="28" t="n">
         <v>2</v>
       </c>
-      <c r="I6" s="28" t="inlineStr">
+      <c r="J6" s="28" t="inlineStr">
         <is>
           <t>RatioBp,2000</t>
         </is>
       </c>
-      <c r="J6" s="28" t="inlineStr">
+      <c r="K6" s="28" t="inlineStr">
         <is>
           <t>Null,0,0</t>
         </is>
       </c>
-      <c r="K6" s="28" t="n">
+      <c r="L6" s="28" t="n">
         <v>3</v>
       </c>
-      <c r="L6" s="28" t="n">
+      <c r="M6" s="28" t="n">
         <v>100</v>
       </c>
     </row>
@@ -3265,28 +3295,33 @@
           <t>0,</t>
         </is>
       </c>
-      <c r="G7" s="28" t="inlineStr">
+      <c r="G7" s="11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H7" s="28" t="inlineStr">
         <is>
           <t>Projectile</t>
         </is>
       </c>
-      <c r="H7" s="28" t="n">
+      <c r="I7" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="I7" s="28" t="inlineStr">
+      <c r="J7" s="28" t="inlineStr">
         <is>
           <t>Int,6003</t>
         </is>
       </c>
-      <c r="J7" s="28" t="inlineStr">
+      <c r="K7" s="28" t="inlineStr">
         <is>
           <t>Null,0,0</t>
         </is>
       </c>
-      <c r="K7" s="28" t="n">
+      <c r="L7" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="L7" s="28" t="n">
+      <c r="M7" s="28" t="n">
         <v>100</v>
       </c>
     </row>
@@ -3315,28 +3350,33 @@
           <t>0,</t>
         </is>
       </c>
-      <c r="G8" s="28" t="inlineStr">
+      <c r="G8" s="11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H8" s="28" t="inlineStr">
         <is>
           <t>Projectile</t>
         </is>
       </c>
-      <c r="H8" s="28" t="n">
+      <c r="I8" s="28" t="n">
         <v>3</v>
       </c>
-      <c r="I8" s="28" t="inlineStr">
+      <c r="J8" s="28" t="inlineStr">
         <is>
           <t>Int,1200</t>
         </is>
       </c>
-      <c r="J8" s="28" t="inlineStr">
+      <c r="K8" s="28" t="inlineStr">
         <is>
           <t>Null,0,0</t>
         </is>
       </c>
-      <c r="K8" s="28" t="n">
+      <c r="L8" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="L8" s="28" t="n">
+      <c r="M8" s="28" t="n">
         <v>100</v>
       </c>
     </row>
@@ -3365,29 +3405,142 @@
           <t>0,</t>
         </is>
       </c>
-      <c r="G9" s="28" t="inlineStr">
+      <c r="G9" s="11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H9" s="28" t="inlineStr">
         <is>
           <t>Projectile</t>
         </is>
       </c>
-      <c r="H9" s="28" t="n">
+      <c r="I9" s="28" t="n">
         <v>2</v>
       </c>
-      <c r="I9" s="28" t="inlineStr">
+      <c r="J9" s="28" t="inlineStr">
         <is>
           <t>Int,1</t>
         </is>
       </c>
-      <c r="J9" s="28" t="inlineStr">
+      <c r="K9" s="28" t="inlineStr">
         <is>
           <t>Null,0,0</t>
         </is>
       </c>
-      <c r="K9" s="28" t="n">
+      <c r="L9" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="L9" s="28" t="n">
+      <c r="M9" s="28" t="n">
         <v>100</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="11" t="n">
+        <v>9201</v>
+      </c>
+      <c r="C10" s="11" t="inlineStr">
+        <is>
+          <t>????</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
+          <t>????????????????</t>
+        </is>
+      </c>
+      <c r="E10" s="11" t="inlineStr">
+        <is>
+          <t>Hero,None,None,None,</t>
+        </is>
+      </c>
+      <c r="F10" s="11" t="inlineStr">
+        <is>
+          <t>0,</t>
+        </is>
+      </c>
+      <c r="G10" s="11" t="inlineStr">
+        <is>
+          <t>OnSkillCast</t>
+        </is>
+      </c>
+      <c r="H10" s="11" t="inlineStr">
+        <is>
+          <t>Trigger</t>
+        </is>
+      </c>
+      <c r="I10" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" s="11" t="inlineStr">
+        <is>
+          <t>Int,1</t>
+        </is>
+      </c>
+      <c r="K10" s="11" t="inlineStr">
+        <is>
+          <t>Damage,3001,10000</t>
+        </is>
+      </c>
+      <c r="L10" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" s="11" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="n">
+        <v>9202</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>????</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>????????????????????</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Hero,None,None,None,</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>0,2002</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>OnProjectileHit</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Trigger</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Int,1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Damage,3001,10000</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/Excels/Excels/B-Battle_战斗表.xlsx
+++ b/Excels/Excels/B-Battle_战斗表.xlsx
@@ -2875,7 +2875,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:T16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" style="12" min="1" max="1"/>
@@ -2958,6 +2958,41 @@
           <t>weight</t>
         </is>
       </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>iconKey</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>rarity</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>tags</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>conflictTags</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>requireEnhancementIds</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>excludeEnhancementIds</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>nextEnhancementIds</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="23" t="inlineStr">
@@ -3025,6 +3060,41 @@
           <t>int</t>
         </is>
       </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Battle.EnhancementRarity</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>(array#sep=|),string</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>(array#sep=|),string</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>(array#sep=|),int</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>(array#sep=|),int</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>(array#sep=|),int</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="25" t="inlineStr">
@@ -3092,6 +3162,41 @@
           <t>c</t>
         </is>
       </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="27" t="inlineStr">
@@ -3157,6 +3262,41 @@
       <c r="M4" s="27" t="inlineStr">
         <is>
           <t>权重</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>??Key</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>??</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>??</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>????</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>????</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>????</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>????</t>
         </is>
       </c>
     </row>
@@ -3214,6 +3354,29 @@
       <c r="M5" s="28" t="n">
         <v>100</v>
       </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>enhance_multi_arrow</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>??|??</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>9011</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="28" t="n"/>
@@ -3269,6 +3432,29 @@
       <c r="M6" s="28" t="n">
         <v>100</v>
       </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>enhance_rapid_shot</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>??|??</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>9012</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="28" t="n"/>
@@ -3324,6 +3510,33 @@
       <c r="M7" s="28" t="n">
         <v>100</v>
       </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>enhance_fireball_arrow</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>??|??|??</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>????</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>9013</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="28" t="n"/>
@@ -3379,6 +3592,29 @@
       <c r="M8" s="28" t="n">
         <v>100</v>
       </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>enhance_blast_arrow</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>??|??</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>9014</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="28" t="n"/>
@@ -3434,6 +3670,29 @@
       <c r="M9" s="28" t="n">
         <v>100</v>
       </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>enhance_pierce_arrow</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>??|??</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>9015</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="B10" s="11" t="n">
@@ -3488,60 +3747,483 @@
       <c r="M10" s="11" t="n">
         <v>10</v>
       </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>enhance_power_draw</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>??|??</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="B11" t="n">
+      <c r="B11" s="11" t="n">
         <v>9202</v>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="11" t="inlineStr">
         <is>
           <t>????</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="11" t="inlineStr">
         <is>
           <t>????????????????????</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E11" s="11" t="inlineStr">
         <is>
           <t>Hero,None,None,None,</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F11" s="11" t="inlineStr">
         <is>
           <t>0,2002</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G11" s="11" t="inlineStr">
         <is>
           <t>OnProjectileHit</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H11" s="11" t="inlineStr">
         <is>
           <t>Trigger</t>
         </is>
       </c>
-      <c r="I11" t="n">
+      <c r="I11" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J11" s="11" t="inlineStr">
         <is>
           <t>Int,1</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="K11" s="11" t="inlineStr">
         <is>
           <t>Damage,3001,10000</t>
         </is>
       </c>
-      <c r="L11" t="n">
+      <c r="L11" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="M11" t="n">
+      <c r="M11" s="11" t="n">
         <v>10</v>
       </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>enhance_chase_arrow</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>??|??|??</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="B12" t="n">
+        <v>9011</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>??? II</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>??????????????</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Hero,None,None,None,</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>0,</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Int,1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Null,0,0</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>60</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>enhance_multi_arrow_2</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>??|??</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>9001</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="B13" t="n">
+        <v>9012</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>????</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>????????????20%?</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Hero,None,None,None,</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>0,</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>2</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>RatioBp,2000</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Null,0,0</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>60</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>enhance_rapid_shot_2</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>??|??</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>9002</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="B14" t="n">
+        <v>9013</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>????</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>??????????????</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Hero,None,None,None,</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>0,</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>OnProjectileHit</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Trigger</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Int,1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Damage,3003,10000</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" t="n">
+        <v>50</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>enhance_fireball_arrow_2</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>??|??|??</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>9003</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="B15" t="n">
+        <v>9014</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>??? II</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>?????????????</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Hero,None,None,None,</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>0,</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Projectile</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>3</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Int,600</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Null,0,0</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" t="n">
+        <v>60</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>enhance_blast_arrow_2</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>??|??</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>9004</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="B16" t="n">
+        <v>9015</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>??? II</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>????????????1????</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Hero,None,None,None,</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>0,</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Projectile</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>2</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Int,1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Null,0,0</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" t="n">
+        <v>60</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>enhance_pierce_arrow_2</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>??|??</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>9005</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Excels/Excels/B-Battle_战斗表.xlsx
+++ b/Excels/Excels/B-Battle_战斗表.xlsx
@@ -2958,37 +2958,37 @@
           <t>weight</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="11" t="inlineStr">
         <is>
           <t>iconKey</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="11" t="inlineStr">
         <is>
           <t>rarity</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="11" t="inlineStr">
         <is>
           <t>tags</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="11" t="inlineStr">
         <is>
           <t>conflictTags</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="11" t="inlineStr">
         <is>
           <t>requireEnhancementIds</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="11" t="inlineStr">
         <is>
           <t>excludeEnhancementIds</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="11" t="inlineStr">
         <is>
           <t>nextEnhancementIds</t>
         </is>
@@ -3060,37 +3060,37 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="N2" s="11" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="O2" s="11" t="inlineStr">
         <is>
           <t>Battle.EnhancementRarity</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="P2" s="11" t="inlineStr">
         <is>
           <t>(array#sep=|),string</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Q2" s="11" t="inlineStr">
         <is>
           <t>(array#sep=|),string</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="R2" s="11" t="inlineStr">
         <is>
           <t>(array#sep=|),int</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="S2" s="11" t="inlineStr">
         <is>
           <t>(array#sep=|),int</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="T2" s="11" t="inlineStr">
         <is>
           <t>(array#sep=|),int</t>
         </is>
@@ -3162,37 +3162,37 @@
           <t>c</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
+      <c r="N3" s="11" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="O3" s="11" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="P3" s="11" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="Q3" s="11" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="R3" s="11" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="S3" s="11" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="T3" s="11" t="inlineStr">
         <is>
           <t>c</t>
         </is>
@@ -3264,37 +3264,37 @@
           <t>权重</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="N4" s="11" t="inlineStr">
         <is>
           <t>??Key</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="O4" s="11" t="inlineStr">
         <is>
           <t>??</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="P4" s="11" t="inlineStr">
         <is>
           <t>??</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="Q4" s="11" t="inlineStr">
         <is>
           <t>????</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="R4" s="11" t="inlineStr">
         <is>
           <t>????</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="S4" s="11" t="inlineStr">
         <is>
           <t>????</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="T4" s="11" t="inlineStr">
         <is>
           <t>????</t>
         </is>
@@ -3317,7 +3317,7 @@
       </c>
       <c r="E5" s="28" t="inlineStr">
         <is>
-          <t>Hero,None,None,None,</t>
+          <t>Hero,None,None,None,Player,</t>
         </is>
       </c>
       <c r="F5" s="28" t="inlineStr">
@@ -3354,25 +3354,25 @@
       <c r="M5" s="28" t="n">
         <v>100</v>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="N5" s="11" t="inlineStr">
         <is>
           <t>enhance_multi_arrow</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="O5" s="11" t="inlineStr">
         <is>
           <t>Common</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="P5" s="11" t="inlineStr">
         <is>
           <t>??|??</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr">
+      <c r="Q5" s="11" t="inlineStr"/>
+      <c r="R5" s="11" t="inlineStr"/>
+      <c r="S5" s="11" t="inlineStr"/>
+      <c r="T5" s="11" t="inlineStr">
         <is>
           <t>9011</t>
         </is>
@@ -3395,7 +3395,7 @@
       </c>
       <c r="E6" s="28" t="inlineStr">
         <is>
-          <t>Hero,None,None,None,</t>
+          <t>Hero,None,None,None,Player,</t>
         </is>
       </c>
       <c r="F6" s="28" t="inlineStr">
@@ -3432,25 +3432,25 @@
       <c r="M6" s="28" t="n">
         <v>100</v>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="N6" s="11" t="inlineStr">
         <is>
           <t>enhance_rapid_shot</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="O6" s="11" t="inlineStr">
         <is>
           <t>Common</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="P6" s="11" t="inlineStr">
         <is>
           <t>??|??</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr">
+      <c r="Q6" s="11" t="inlineStr"/>
+      <c r="R6" s="11" t="inlineStr"/>
+      <c r="S6" s="11" t="inlineStr"/>
+      <c r="T6" s="11" t="inlineStr">
         <is>
           <t>9012</t>
         </is>
@@ -3473,7 +3473,7 @@
       </c>
       <c r="E7" s="28" t="inlineStr">
         <is>
-          <t>Hero,None,None,None,</t>
+          <t>Hero,None,None,None,Player,</t>
         </is>
       </c>
       <c r="F7" s="28" t="inlineStr">
@@ -3510,29 +3510,29 @@
       <c r="M7" s="28" t="n">
         <v>100</v>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="N7" s="11" t="inlineStr">
         <is>
           <t>enhance_fireball_arrow</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="O7" s="11" t="inlineStr">
         <is>
           <t>Rare</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="P7" s="11" t="inlineStr">
         <is>
           <t>??|??|??</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Q7" s="11" t="inlineStr">
         <is>
           <t>????</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr">
+      <c r="R7" s="11" t="inlineStr"/>
+      <c r="S7" s="11" t="inlineStr"/>
+      <c r="T7" s="11" t="inlineStr">
         <is>
           <t>9013</t>
         </is>
@@ -3555,7 +3555,7 @@
       </c>
       <c r="E8" s="28" t="inlineStr">
         <is>
-          <t>Hero,None,None,None,</t>
+          <t>Hero,None,None,None,Player,</t>
         </is>
       </c>
       <c r="F8" s="28" t="inlineStr">
@@ -3592,25 +3592,25 @@
       <c r="M8" s="28" t="n">
         <v>100</v>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="N8" s="11" t="inlineStr">
         <is>
           <t>enhance_blast_arrow</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="O8" s="11" t="inlineStr">
         <is>
           <t>Rare</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="P8" s="11" t="inlineStr">
         <is>
           <t>??|??</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr">
+      <c r="Q8" s="11" t="inlineStr"/>
+      <c r="R8" s="11" t="inlineStr"/>
+      <c r="S8" s="11" t="inlineStr"/>
+      <c r="T8" s="11" t="inlineStr">
         <is>
           <t>9014</t>
         </is>
@@ -3633,7 +3633,7 @@
       </c>
       <c r="E9" s="28" t="inlineStr">
         <is>
-          <t>Hero,None,None,None,</t>
+          <t>Hero,None,None,None,Player,</t>
         </is>
       </c>
       <c r="F9" s="28" t="inlineStr">
@@ -3670,25 +3670,25 @@
       <c r="M9" s="28" t="n">
         <v>100</v>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="N9" s="11" t="inlineStr">
         <is>
           <t>enhance_pierce_arrow</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="O9" s="11" t="inlineStr">
         <is>
           <t>Common</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="P9" s="11" t="inlineStr">
         <is>
           <t>??|??</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr">
+      <c r="Q9" s="11" t="inlineStr"/>
+      <c r="R9" s="11" t="inlineStr"/>
+      <c r="S9" s="11" t="inlineStr"/>
+      <c r="T9" s="11" t="inlineStr">
         <is>
           <t>9015</t>
         </is>
@@ -3710,7 +3710,7 @@
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>Hero,None,None,None,</t>
+          <t>Hero,None,None,None,Player,</t>
         </is>
       </c>
       <c r="F10" s="11" t="inlineStr">
@@ -3747,25 +3747,25 @@
       <c r="M10" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="N10" s="11" t="inlineStr">
         <is>
           <t>enhance_power_draw</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="O10" s="11" t="inlineStr">
         <is>
           <t>Rare</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="P10" s="11" t="inlineStr">
         <is>
           <t>??|??</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
+      <c r="Q10" s="11" t="inlineStr"/>
+      <c r="R10" s="11" t="inlineStr"/>
+      <c r="S10" s="11" t="inlineStr"/>
+      <c r="T10" s="11" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="B11" s="11" t="n">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>Hero,None,None,None,</t>
+          <t>Hero,None,None,None,Player,</t>
         </is>
       </c>
       <c r="F11" s="11" t="inlineStr">
@@ -3820,410 +3820,410 @@
       <c r="M11" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="N11" s="11" t="inlineStr">
         <is>
           <t>enhance_chase_arrow</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="O11" s="11" t="inlineStr">
         <is>
           <t>Rare</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="P11" s="11" t="inlineStr">
         <is>
           <t>??|??|??</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
+      <c r="Q11" s="11" t="inlineStr"/>
+      <c r="R11" s="11" t="inlineStr"/>
+      <c r="S11" s="11" t="inlineStr"/>
+      <c r="T11" s="11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="B12" t="n">
+      <c r="B12" s="11" t="n">
         <v>9011</v>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="11" t="inlineStr">
         <is>
           <t>??? II</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" s="11" t="inlineStr">
         <is>
           <t>??????????????</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Hero,None,None,None,</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
+      <c r="E12" s="11" t="inlineStr">
+        <is>
+          <t>Hero,None,None,None,Player,</t>
+        </is>
+      </c>
+      <c r="F12" s="11" t="inlineStr">
         <is>
           <t>0,</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G12" s="11" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H12" s="11" t="inlineStr">
         <is>
           <t>Skill</t>
         </is>
       </c>
-      <c r="I12" t="n">
+      <c r="I12" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="J12" s="11" t="inlineStr">
         <is>
           <t>Int,1</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="K12" s="11" t="inlineStr">
         <is>
           <t>Null,0,0</t>
         </is>
       </c>
-      <c r="L12" t="n">
+      <c r="L12" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="M12" t="n">
+      <c r="M12" s="11" t="n">
         <v>60</v>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="N12" s="11" t="inlineStr">
         <is>
           <t>enhance_multi_arrow_2</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="O12" s="11" t="inlineStr">
         <is>
           <t>Rare</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="P12" s="11" t="inlineStr">
         <is>
           <t>??|??</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr">
+      <c r="Q12" s="11" t="inlineStr"/>
+      <c r="R12" s="11" t="inlineStr">
         <is>
           <t>9001</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr"/>
+      <c r="S12" s="11" t="inlineStr"/>
+      <c r="T12" s="11" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="B13" t="n">
+      <c r="B13" s="11" t="n">
         <v>9012</v>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="11" t="inlineStr">
         <is>
           <t>????</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" s="11" t="inlineStr">
         <is>
           <t>????????????20%?</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Hero,None,None,None,</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
+      <c r="E13" s="11" t="inlineStr">
+        <is>
+          <t>Hero,None,None,None,Player,</t>
+        </is>
+      </c>
+      <c r="F13" s="11" t="inlineStr">
         <is>
           <t>0,</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G13" s="11" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H13" s="11" t="inlineStr">
         <is>
           <t>Skill</t>
         </is>
       </c>
-      <c r="I13" t="n">
+      <c r="I13" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="J13" s="11" t="inlineStr">
         <is>
           <t>RatioBp,2000</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="K13" s="11" t="inlineStr">
         <is>
           <t>Null,0,0</t>
         </is>
       </c>
-      <c r="L13" t="n">
+      <c r="L13" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="M13" t="n">
+      <c r="M13" s="11" t="n">
         <v>60</v>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="N13" s="11" t="inlineStr">
         <is>
           <t>enhance_rapid_shot_2</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="O13" s="11" t="inlineStr">
         <is>
           <t>Rare</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="P13" s="11" t="inlineStr">
         <is>
           <t>??|??</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr">
+      <c r="Q13" s="11" t="inlineStr"/>
+      <c r="R13" s="11" t="inlineStr">
         <is>
           <t>9002</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr"/>
+      <c r="S13" s="11" t="inlineStr"/>
+      <c r="T13" s="11" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="B14" t="n">
+      <c r="B14" s="11" t="n">
         <v>9013</v>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="11" t="inlineStr">
         <is>
           <t>????</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" s="11" t="inlineStr">
         <is>
           <t>??????????????</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Hero,None,None,None,</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
+      <c r="E14" s="11" t="inlineStr">
+        <is>
+          <t>Hero,None,None,None,Player,</t>
+        </is>
+      </c>
+      <c r="F14" s="11" t="inlineStr">
         <is>
           <t>0,</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G14" s="11" t="inlineStr">
         <is>
           <t>OnProjectileHit</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="H14" s="11" t="inlineStr">
         <is>
           <t>Trigger</t>
         </is>
       </c>
-      <c r="I14" t="n">
+      <c r="I14" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="J14" s="11" t="inlineStr">
         <is>
           <t>Int,1</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="K14" s="11" t="inlineStr">
         <is>
           <t>Damage,3003,10000</t>
         </is>
       </c>
-      <c r="L14" t="n">
+      <c r="L14" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="M14" t="n">
+      <c r="M14" s="11" t="n">
         <v>50</v>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="N14" s="11" t="inlineStr">
         <is>
           <t>enhance_fireball_arrow_2</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="O14" s="11" t="inlineStr">
         <is>
           <t>Epic</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="P14" s="11" t="inlineStr">
         <is>
           <t>??|??|??</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr">
+      <c r="Q14" s="11" t="inlineStr"/>
+      <c r="R14" s="11" t="inlineStr">
         <is>
           <t>9003</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
+      <c r="S14" s="11" t="inlineStr"/>
+      <c r="T14" s="11" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="B15" t="n">
+      <c r="B15" s="11" t="n">
         <v>9014</v>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="11" t="inlineStr">
         <is>
           <t>??? II</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" s="11" t="inlineStr">
         <is>
           <t>?????????????</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Hero,None,None,None,</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
+      <c r="E15" s="11" t="inlineStr">
+        <is>
+          <t>Hero,None,None,None,Player,</t>
+        </is>
+      </c>
+      <c r="F15" s="11" t="inlineStr">
         <is>
           <t>0,</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G15" s="11" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="H15" s="11" t="inlineStr">
         <is>
           <t>Projectile</t>
         </is>
       </c>
-      <c r="I15" t="n">
+      <c r="I15" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="J15" s="11" t="inlineStr">
         <is>
           <t>Int,600</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="K15" s="11" t="inlineStr">
         <is>
           <t>Null,0,0</t>
         </is>
       </c>
-      <c r="L15" t="n">
+      <c r="L15" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="M15" t="n">
+      <c r="M15" s="11" t="n">
         <v>60</v>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="N15" s="11" t="inlineStr">
         <is>
           <t>enhance_blast_arrow_2</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="O15" s="11" t="inlineStr">
         <is>
           <t>Rare</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
+      <c r="P15" s="11" t="inlineStr">
         <is>
           <t>??|??</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr">
+      <c r="Q15" s="11" t="inlineStr"/>
+      <c r="R15" s="11" t="inlineStr">
         <is>
           <t>9004</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr"/>
+      <c r="S15" s="11" t="inlineStr"/>
+      <c r="T15" s="11" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="B16" t="n">
+      <c r="B16" s="11" t="n">
         <v>9015</v>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" s="11" t="inlineStr">
         <is>
           <t>??? II</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D16" s="11" t="inlineStr">
         <is>
           <t>????????????1????</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Hero,None,None,None,</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
+      <c r="E16" s="11" t="inlineStr">
+        <is>
+          <t>Hero,None,None,None,Player,</t>
+        </is>
+      </c>
+      <c r="F16" s="11" t="inlineStr">
         <is>
           <t>0,</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G16" s="11" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="H16" s="11" t="inlineStr">
         <is>
           <t>Projectile</t>
         </is>
       </c>
-      <c r="I16" t="n">
+      <c r="I16" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="J16" s="11" t="inlineStr">
         <is>
           <t>Int,1</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="K16" s="11" t="inlineStr">
         <is>
           <t>Null,0,0</t>
         </is>
       </c>
-      <c r="L16" t="n">
+      <c r="L16" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="M16" t="n">
+      <c r="M16" s="11" t="n">
         <v>60</v>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="N16" s="11" t="inlineStr">
         <is>
           <t>enhance_pierce_arrow_2</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
+      <c r="O16" s="11" t="inlineStr">
         <is>
           <t>Rare</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr">
+      <c r="P16" s="11" t="inlineStr">
         <is>
           <t>??|??</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr">
+      <c r="Q16" s="11" t="inlineStr"/>
+      <c r="R16" s="11" t="inlineStr">
         <is>
           <t>9005</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr"/>
-      <c r="T16" t="inlineStr"/>
+      <c r="S16" s="11" t="inlineStr"/>
+      <c r="T16" s="11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
